--- a/source_data/Extended_Data_Fig_4_source_data.xlsx
+++ b/source_data/Extended_Data_Fig_4_source_data.xlsx
@@ -459,7 +459,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Sixty bootstrap samples, each of 4,690 city records drawn with replacement (80% of the sample size), are clustered, and their predictions for all cities are compared with the full-data six-cluster solution and the six rule-defined patterns. Black dots and bars mark medians and interquartile ranges. Stability of a clustering and its similarity to policy-oriented diagnostic types need not coincide.</t>
+          <t>Sixty bootstrap samples, each of 4,690 city records drawn with replacement (80% of the sample size), are clustered, and their predictions for all cities are compared with the full-data six-cluster solution and the six rule-defined patterns. Black dots and bars mark medians and interquartile ranges.</t>
         </is>
       </c>
     </row>
@@ -534,13 +534,13 @@
         <v>0.8</v>
       </c>
       <c r="C2" t="n">
-        <v>0.9158417487182644</v>
+        <v>0.9161219859029044</v>
       </c>
       <c r="D2" t="n">
-        <v>0.2821879862783488</v>
+        <v>0.2858742402181335</v>
       </c>
       <c r="E2" t="n">
-        <v>0.4314462363342931</v>
+        <v>0.4343836857061428</v>
       </c>
     </row>
     <row r="3">
@@ -551,13 +551,13 @@
         <v>0.8</v>
       </c>
       <c r="C3" t="n">
-        <v>0.7914476907407381</v>
+        <v>0.8204693482203995</v>
       </c>
       <c r="D3" t="n">
-        <v>0.309241136043799</v>
+        <v>0.3068122200881878</v>
       </c>
       <c r="E3" t="n">
-        <v>0.4462401127287854</v>
+        <v>0.4397282667100444</v>
       </c>
     </row>
     <row r="4">
@@ -568,13 +568,13 @@
         <v>0.8</v>
       </c>
       <c r="C4" t="n">
-        <v>0.9641697929308544</v>
+        <v>0.9753550974445528</v>
       </c>
       <c r="D4" t="n">
-        <v>0.2908605364291312</v>
+        <v>0.287182406995806</v>
       </c>
       <c r="E4" t="n">
-        <v>0.4293669742786675</v>
+        <v>0.4277469681277209</v>
       </c>
     </row>
     <row r="5">
@@ -585,13 +585,13 @@
         <v>0.8</v>
       </c>
       <c r="C5" t="n">
-        <v>0.8467949627310639</v>
+        <v>0.8085265741188831</v>
       </c>
       <c r="D5" t="n">
-        <v>0.2973517205592486</v>
+        <v>0.2984107383409975</v>
       </c>
       <c r="E5" t="n">
-        <v>0.4368075144758657</v>
+        <v>0.439122365675493</v>
       </c>
     </row>
     <row r="6">
@@ -602,13 +602,13 @@
         <v>0.8</v>
       </c>
       <c r="C6" t="n">
-        <v>0.6175237194829971</v>
+        <v>0.6620976170014243</v>
       </c>
       <c r="D6" t="n">
-        <v>0.2541894806965443</v>
+        <v>0.259736529222039</v>
       </c>
       <c r="E6" t="n">
-        <v>0.4244698764979355</v>
+        <v>0.4307768741760172</v>
       </c>
     </row>
     <row r="7">
@@ -619,13 +619,13 @@
         <v>0.8</v>
       </c>
       <c r="C7" t="n">
-        <v>0.9427081504609848</v>
+        <v>0.9141562197527152</v>
       </c>
       <c r="D7" t="n">
-        <v>0.2807651681801612</v>
+        <v>0.2789878177315078</v>
       </c>
       <c r="E7" t="n">
-        <v>0.4246631340291006</v>
+        <v>0.4257229164937756</v>
       </c>
     </row>
     <row r="8">
@@ -636,13 +636,13 @@
         <v>0.8</v>
       </c>
       <c r="C8" t="n">
-        <v>0.8045314333628331</v>
+        <v>0.8024678605650037</v>
       </c>
       <c r="D8" t="n">
-        <v>0.3053745293083253</v>
+        <v>0.3057008816258608</v>
       </c>
       <c r="E8" t="n">
-        <v>0.441065963412053</v>
+        <v>0.441825504544134</v>
       </c>
     </row>
     <row r="9">
@@ -653,13 +653,13 @@
         <v>0.8</v>
       </c>
       <c r="C9" t="n">
-        <v>0.8453249950321751</v>
+        <v>0.8745377958290435</v>
       </c>
       <c r="D9" t="n">
-        <v>0.3022563725022994</v>
+        <v>0.3000852069289328</v>
       </c>
       <c r="E9" t="n">
-        <v>0.4368795312171378</v>
+        <v>0.4337608015346288</v>
       </c>
     </row>
     <row r="10">
@@ -670,13 +670,13 @@
         <v>0.8</v>
       </c>
       <c r="C10" t="n">
-        <v>0.9463338229630566</v>
+        <v>0.9262674314416296</v>
       </c>
       <c r="D10" t="n">
-        <v>0.2861437990839439</v>
+        <v>0.2861907606194014</v>
       </c>
       <c r="E10" t="n">
-        <v>0.4268458630078669</v>
+        <v>0.4290087604692454</v>
       </c>
     </row>
     <row r="11">
@@ -687,13 +687,13 @@
         <v>0.8</v>
       </c>
       <c r="C11" t="n">
-        <v>0.9805053115655394</v>
+        <v>0.9580199287240658</v>
       </c>
       <c r="D11" t="n">
-        <v>0.2850927370275202</v>
+        <v>0.283637403957246</v>
       </c>
       <c r="E11" t="n">
-        <v>0.4270182905423896</v>
+        <v>0.4277335550138672</v>
       </c>
     </row>
     <row r="12">
@@ -704,13 +704,13 @@
         <v>0.8</v>
       </c>
       <c r="C12" t="n">
-        <v>0.946876861878629</v>
+        <v>0.945805281145616</v>
       </c>
       <c r="D12" t="n">
-        <v>0.2898585875946277</v>
+        <v>0.2903049268260085</v>
       </c>
       <c r="E12" t="n">
-        <v>0.4328342170747998</v>
+        <v>0.432865670012279</v>
       </c>
     </row>
     <row r="13">
@@ -721,13 +721,13 @@
         <v>0.8</v>
       </c>
       <c r="C13" t="n">
-        <v>0.9531228377235288</v>
+        <v>0.8604699102048904</v>
       </c>
       <c r="D13" t="n">
-        <v>0.2860518260825223</v>
+        <v>0.3052790046514316</v>
       </c>
       <c r="E13" t="n">
-        <v>0.4290035835045327</v>
+        <v>0.4383490322312509</v>
       </c>
     </row>
     <row r="14">
@@ -738,13 +738,13 @@
         <v>0.8</v>
       </c>
       <c r="C14" t="n">
-        <v>0.9364439599296672</v>
+        <v>0.9523635809902796</v>
       </c>
       <c r="D14" t="n">
-        <v>0.2893291790929535</v>
+        <v>0.2903304628529451</v>
       </c>
       <c r="E14" t="n">
-        <v>0.4277930642712128</v>
+        <v>0.4288243165891627</v>
       </c>
     </row>
     <row r="15">
@@ -755,13 +755,13 @@
         <v>0.8</v>
       </c>
       <c r="C15" t="n">
-        <v>0.943058988638241</v>
+        <v>0.951123705449997</v>
       </c>
       <c r="D15" t="n">
-        <v>0.2891611599455567</v>
+        <v>0.2897314482940205</v>
       </c>
       <c r="E15" t="n">
-        <v>0.4273154335418356</v>
+        <v>0.4287365515412434</v>
       </c>
     </row>
     <row r="16">
@@ -772,13 +772,13 @@
         <v>0.8</v>
       </c>
       <c r="C16" t="n">
-        <v>0.9358173964598698</v>
+        <v>0.939287583132413</v>
       </c>
       <c r="D16" t="n">
-        <v>0.2841481455867652</v>
+        <v>0.2841672104605685</v>
       </c>
       <c r="E16" t="n">
-        <v>0.4288786049839891</v>
+        <v>0.4282864597489763</v>
       </c>
     </row>
     <row r="17">
@@ -789,13 +789,13 @@
         <v>0.8</v>
       </c>
       <c r="C17" t="n">
-        <v>0.9625537840315328</v>
+        <v>0.9619946480980124</v>
       </c>
       <c r="D17" t="n">
-        <v>0.2879472679199221</v>
+        <v>0.2882990206255433</v>
       </c>
       <c r="E17" t="n">
-        <v>0.4306439322190797</v>
+        <v>0.4307040898746748</v>
       </c>
     </row>
     <row r="18">
@@ -806,13 +806,13 @@
         <v>0.8</v>
       </c>
       <c r="C18" t="n">
-        <v>0.960646984536252</v>
+        <v>0.9689735791805932</v>
       </c>
       <c r="D18" t="n">
-        <v>0.2925157513591571</v>
+        <v>0.2934776358613374</v>
       </c>
       <c r="E18" t="n">
-        <v>0.4303017841713044</v>
+        <v>0.4316229914080634</v>
       </c>
     </row>
     <row r="19">
@@ -823,13 +823,13 @@
         <v>0.8</v>
       </c>
       <c r="C19" t="n">
-        <v>0.93130147178596</v>
+        <v>0.967982708483994</v>
       </c>
       <c r="D19" t="n">
-        <v>0.2921513500337706</v>
+        <v>0.2888286595384635</v>
       </c>
       <c r="E19" t="n">
-        <v>0.4294087681037821</v>
+        <v>0.4292542672565114</v>
       </c>
     </row>
     <row r="20">
@@ -840,13 +840,13 @@
         <v>0.8</v>
       </c>
       <c r="C20" t="n">
-        <v>0.8618228836807349</v>
+        <v>0.8602344885464744</v>
       </c>
       <c r="D20" t="n">
-        <v>0.3031737981560738</v>
+        <v>0.3047015760787457</v>
       </c>
       <c r="E20" t="n">
-        <v>0.439422778667244</v>
+        <v>0.4407239680352021</v>
       </c>
     </row>
     <row r="21">
@@ -857,13 +857,13 @@
         <v>0.8</v>
       </c>
       <c r="C21" t="n">
-        <v>0.9410597665195199</v>
+        <v>0.9461956841095894</v>
       </c>
       <c r="D21" t="n">
-        <v>0.2849835135967018</v>
+        <v>0.2851675647290373</v>
       </c>
       <c r="E21" t="n">
-        <v>0.4268609848172882</v>
+        <v>0.4276962549677481</v>
       </c>
     </row>
     <row r="22">
@@ -874,13 +874,13 @@
         <v>0.8</v>
       </c>
       <c r="C22" t="n">
-        <v>0.9332473608795452</v>
+        <v>0.915537749260699</v>
       </c>
       <c r="D22" t="n">
-        <v>0.2827198354578953</v>
+        <v>0.2817909838167129</v>
       </c>
       <c r="E22" t="n">
-        <v>0.4278577127135965</v>
+        <v>0.4282664199210049</v>
       </c>
     </row>
     <row r="23">
@@ -891,13 +891,13 @@
         <v>0.8</v>
       </c>
       <c r="C23" t="n">
-        <v>0.894660538955117</v>
+        <v>0.9691428943745308</v>
       </c>
       <c r="D23" t="n">
-        <v>0.301172933295682</v>
+        <v>0.2927243927837938</v>
       </c>
       <c r="E23" t="n">
-        <v>0.4361070165111302</v>
+        <v>0.4309646782282428</v>
       </c>
     </row>
     <row r="24">
@@ -908,13 +908,13 @@
         <v>0.8</v>
       </c>
       <c r="C24" t="n">
-        <v>0.9729648816180856</v>
+        <v>0.9723095230799798</v>
       </c>
       <c r="D24" t="n">
-        <v>0.2878420423692572</v>
+        <v>0.289213815351938</v>
       </c>
       <c r="E24" t="n">
-        <v>0.4269106390037905</v>
+        <v>0.4279824573597723</v>
       </c>
     </row>
     <row r="25">
@@ -925,13 +925,13 @@
         <v>0.8</v>
       </c>
       <c r="C25" t="n">
-        <v>0.9192570367357842</v>
+        <v>0.8339891853777398</v>
       </c>
       <c r="D25" t="n">
-        <v>0.2807192573988037</v>
+        <v>0.3009194747447803</v>
       </c>
       <c r="E25" t="n">
-        <v>0.4263879472550941</v>
+        <v>0.4387046147730692</v>
       </c>
     </row>
     <row r="26">
@@ -942,13 +942,13 @@
         <v>0.8</v>
       </c>
       <c r="C26" t="n">
-        <v>0.9658688851175474</v>
+        <v>0.9469074424087875</v>
       </c>
       <c r="D26" t="n">
-        <v>0.2865643871776305</v>
+        <v>0.2898589726350476</v>
       </c>
       <c r="E26" t="n">
-        <v>0.4271300698523257</v>
+        <v>0.427518443455325</v>
       </c>
     </row>
     <row r="27">
@@ -959,13 +959,13 @@
         <v>0.8</v>
       </c>
       <c r="C27" t="n">
-        <v>0.953937198868842</v>
+        <v>0.9609302709126046</v>
       </c>
       <c r="D27" t="n">
-        <v>0.2820341261064132</v>
+        <v>0.2832433772462836</v>
       </c>
       <c r="E27" t="n">
-        <v>0.4268735880497888</v>
+        <v>0.426588057233168</v>
       </c>
     </row>
     <row r="28">
@@ -976,13 +976,13 @@
         <v>0.8</v>
       </c>
       <c r="C28" t="n">
-        <v>0.9571655339123428</v>
+        <v>0.8716123166129965</v>
       </c>
       <c r="D28" t="n">
-        <v>0.2943530901754001</v>
+        <v>0.3034978471521925</v>
       </c>
       <c r="E28" t="n">
-        <v>0.4322605611671888</v>
+        <v>0.4383800892827857</v>
       </c>
     </row>
     <row r="29">
@@ -993,13 +993,13 @@
         <v>0.8</v>
       </c>
       <c r="C29" t="n">
-        <v>0.9491008437707668</v>
+        <v>0.9768593272687792</v>
       </c>
       <c r="D29" t="n">
-        <v>0.2833350656089479</v>
+        <v>0.2877122373743875</v>
       </c>
       <c r="E29" t="n">
-        <v>0.4277766745952034</v>
+        <v>0.4271883396333862</v>
       </c>
     </row>
     <row r="30">
@@ -1010,13 +1010,13 @@
         <v>0.8</v>
       </c>
       <c r="C30" t="n">
-        <v>0.9630683389365516</v>
+        <v>0.9592276375162468</v>
       </c>
       <c r="D30" t="n">
-        <v>0.2882137550149198</v>
+        <v>0.2862820348377636</v>
       </c>
       <c r="E30" t="n">
-        <v>0.4281058533728614</v>
+        <v>0.4281698182741449</v>
       </c>
     </row>
     <row r="31">
@@ -1027,13 +1027,13 @@
         <v>0.8</v>
       </c>
       <c r="C31" t="n">
-        <v>0.9071557359861674</v>
+        <v>0.9139533235070556</v>
       </c>
       <c r="D31" t="n">
-        <v>0.2811280175451552</v>
+        <v>0.2822069296916748</v>
       </c>
       <c r="E31" t="n">
-        <v>0.4281817819142839</v>
+        <v>0.4282066907647952</v>
       </c>
     </row>
     <row r="32">
@@ -1044,13 +1044,13 @@
         <v>0.8</v>
       </c>
       <c r="C32" t="n">
-        <v>0.9310870978119876</v>
+        <v>0.935869116984821</v>
       </c>
       <c r="D32" t="n">
-        <v>0.2842385567745837</v>
+        <v>0.2851092429038154</v>
       </c>
       <c r="E32" t="n">
-        <v>0.4305540645343438</v>
+        <v>0.4306192016058723</v>
       </c>
     </row>
     <row r="33">
@@ -1061,13 +1061,13 @@
         <v>0.8</v>
       </c>
       <c r="C33" t="n">
-        <v>0.9530358453068808</v>
+        <v>0.9470245662707278</v>
       </c>
       <c r="D33" t="n">
-        <v>0.2849593763954695</v>
+        <v>0.28608801637366</v>
       </c>
       <c r="E33" t="n">
-        <v>0.4289556745398842</v>
+        <v>0.4305707406847544</v>
       </c>
     </row>
     <row r="34">
@@ -1078,13 +1078,13 @@
         <v>0.8</v>
       </c>
       <c r="C34" t="n">
-        <v>0.8761439548029218</v>
+        <v>0.878092735498231</v>
       </c>
       <c r="D34" t="n">
-        <v>0.2871740303495341</v>
+        <v>0.2866915789638117</v>
       </c>
       <c r="E34" t="n">
-        <v>0.4384626439456108</v>
+        <v>0.4381400330194405</v>
       </c>
     </row>
     <row r="35">
@@ -1095,13 +1095,13 @@
         <v>0.8</v>
       </c>
       <c r="C35" t="n">
-        <v>0.7283047310595333</v>
+        <v>0.8233490488965494</v>
       </c>
       <c r="D35" t="n">
-        <v>0.294402641843068</v>
+        <v>0.3004465484456522</v>
       </c>
       <c r="E35" t="n">
-        <v>0.4393677878324769</v>
+        <v>0.4388623710325218</v>
       </c>
     </row>
     <row r="36">
@@ -1112,13 +1112,13 @@
         <v>0.8</v>
       </c>
       <c r="C36" t="n">
-        <v>0.957594179318321</v>
+        <v>0.959553998124528</v>
       </c>
       <c r="D36" t="n">
-        <v>0.2802236907196957</v>
+        <v>0.2868160502255958</v>
       </c>
       <c r="E36" t="n">
-        <v>0.4240837016372239</v>
+        <v>0.42654761196519</v>
       </c>
     </row>
     <row r="37">
@@ -1129,13 +1129,13 @@
         <v>0.8</v>
       </c>
       <c r="C37" t="n">
-        <v>0.9515952585437024</v>
+        <v>0.958303541367872</v>
       </c>
       <c r="D37" t="n">
-        <v>0.2805722557097047</v>
+        <v>0.2821623579575545</v>
       </c>
       <c r="E37" t="n">
-        <v>0.424605126163442</v>
+        <v>0.4260383541952394</v>
       </c>
     </row>
     <row r="38">
@@ -1146,13 +1146,13 @@
         <v>0.8</v>
       </c>
       <c r="C38" t="n">
-        <v>0.8180030214969375</v>
+        <v>0.928351961854732</v>
       </c>
       <c r="D38" t="n">
-        <v>0.2954155706525888</v>
+        <v>0.2808343233479075</v>
       </c>
       <c r="E38" t="n">
-        <v>0.4384964687676278</v>
+        <v>0.4267899895830556</v>
       </c>
     </row>
     <row r="39">
@@ -1163,13 +1163,13 @@
         <v>0.8</v>
       </c>
       <c r="C39" t="n">
-        <v>0.9674711112104224</v>
+        <v>0.9683313298493704</v>
       </c>
       <c r="D39" t="n">
-        <v>0.2884421404158086</v>
+        <v>0.2892869045015935</v>
       </c>
       <c r="E39" t="n">
-        <v>0.4293818159037573</v>
+        <v>0.4301131037334558</v>
       </c>
     </row>
     <row r="40">
@@ -1180,13 +1180,13 @@
         <v>0.8</v>
       </c>
       <c r="C40" t="n">
-        <v>0.7885060589511936</v>
+        <v>0.7858079987471411</v>
       </c>
       <c r="D40" t="n">
-        <v>0.3066852199844354</v>
+        <v>0.3068686436696718</v>
       </c>
       <c r="E40" t="n">
-        <v>0.4433549056562958</v>
+        <v>0.4433544609799176</v>
       </c>
     </row>
     <row r="41">
@@ -1197,13 +1197,13 @@
         <v>0.8</v>
       </c>
       <c r="C41" t="n">
-        <v>0.9255112271017768</v>
+        <v>0.973199802285044</v>
       </c>
       <c r="D41" t="n">
-        <v>0.292954940227191</v>
+        <v>0.2937243620764343</v>
       </c>
       <c r="E41" t="n">
-        <v>0.438818441413592</v>
+        <v>0.4335926521551829</v>
       </c>
     </row>
     <row r="42">
@@ -1214,13 +1214,13 @@
         <v>0.8</v>
       </c>
       <c r="C42" t="n">
-        <v>0.8815533831737702</v>
+        <v>0.911794746302071</v>
       </c>
       <c r="D42" t="n">
-        <v>0.3029155088717671</v>
+        <v>0.3000652474514945</v>
       </c>
       <c r="E42" t="n">
-        <v>0.437737155352181</v>
+        <v>0.4353396385171832</v>
       </c>
     </row>
     <row r="43">
@@ -1231,13 +1231,13 @@
         <v>0.8</v>
       </c>
       <c r="C43" t="n">
-        <v>0.8594826572053618</v>
+        <v>0.8632261670590698</v>
       </c>
       <c r="D43" t="n">
-        <v>0.3012738238938647</v>
+        <v>0.3006039870002613</v>
       </c>
       <c r="E43" t="n">
-        <v>0.4365056191059741</v>
+        <v>0.4359421123021238</v>
       </c>
     </row>
     <row r="44">
@@ -1248,13 +1248,13 @@
         <v>0.8</v>
       </c>
       <c r="C44" t="n">
-        <v>0.8925916982831131</v>
+        <v>0.905002612437932</v>
       </c>
       <c r="D44" t="n">
-        <v>0.3004185465369382</v>
+        <v>0.3001808536333933</v>
       </c>
       <c r="E44" t="n">
-        <v>0.4340783306943824</v>
+        <v>0.4339102036362373</v>
       </c>
     </row>
     <row r="45">
@@ -1265,13 +1265,13 @@
         <v>0.8</v>
       </c>
       <c r="C45" t="n">
-        <v>0.96337979866881</v>
+        <v>0.9635999846925928</v>
       </c>
       <c r="D45" t="n">
-        <v>0.2878867892615806</v>
+        <v>0.287976490115789</v>
       </c>
       <c r="E45" t="n">
-        <v>0.4286679411442502</v>
+        <v>0.4285493650808443</v>
       </c>
     </row>
     <row r="46">
@@ -1282,13 +1282,13 @@
         <v>0.8</v>
       </c>
       <c r="C46" t="n">
-        <v>0.7887732564816792</v>
+        <v>0.7917409383168327</v>
       </c>
       <c r="D46" t="n">
-        <v>0.298838651487514</v>
+        <v>0.2999522175262091</v>
       </c>
       <c r="E46" t="n">
-        <v>0.4419820365037742</v>
+        <v>0.4426381250560036</v>
       </c>
     </row>
     <row r="47">
@@ -1299,13 +1299,13 @@
         <v>0.8</v>
       </c>
       <c r="C47" t="n">
-        <v>0.8012541883008504</v>
+        <v>0.7990177602125333</v>
       </c>
       <c r="D47" t="n">
-        <v>0.3020249711891468</v>
+        <v>0.3022359803047246</v>
       </c>
       <c r="E47" t="n">
-        <v>0.441752241289524</v>
+        <v>0.4417896871894063</v>
       </c>
     </row>
     <row r="48">
@@ -1316,13 +1316,13 @@
         <v>0.8</v>
       </c>
       <c r="C48" t="n">
-        <v>0.9258798649311504</v>
+        <v>0.9275307242865172</v>
       </c>
       <c r="D48" t="n">
-        <v>0.2889372644014428</v>
+        <v>0.2905210127918065</v>
       </c>
       <c r="E48" t="n">
-        <v>0.4284616659707152</v>
+        <v>0.4295495415575218</v>
       </c>
     </row>
     <row r="49">
@@ -1333,13 +1333,13 @@
         <v>0.8</v>
       </c>
       <c r="C49" t="n">
-        <v>0.8469888869851944</v>
+        <v>0.8489519369143951</v>
       </c>
       <c r="D49" t="n">
-        <v>0.293788587890593</v>
+        <v>0.2941420673930875</v>
       </c>
       <c r="E49" t="n">
-        <v>0.4453498274254008</v>
+        <v>0.4456464141477707</v>
       </c>
     </row>
     <row r="50">
@@ -1350,13 +1350,13 @@
         <v>0.8</v>
       </c>
       <c r="C50" t="n">
-        <v>0.9368958690321992</v>
+        <v>0.9396830582040844</v>
       </c>
       <c r="D50" t="n">
-        <v>0.2927602791195889</v>
+        <v>0.2937649646181905</v>
       </c>
       <c r="E50" t="n">
-        <v>0.4302964237989349</v>
+        <v>0.4310450576900237</v>
       </c>
     </row>
     <row r="51">
@@ -1367,13 +1367,13 @@
         <v>0.8</v>
       </c>
       <c r="C51" t="n">
-        <v>0.8981599553892229</v>
+        <v>0.8991077204721224</v>
       </c>
       <c r="D51" t="n">
-        <v>0.297798683564316</v>
+        <v>0.2987019936485371</v>
       </c>
       <c r="E51" t="n">
-        <v>0.4337732844462773</v>
+        <v>0.4346378260873308</v>
       </c>
     </row>
     <row r="52">
@@ -1384,13 +1384,13 @@
         <v>0.8</v>
       </c>
       <c r="C52" t="n">
-        <v>0.9537121043555294</v>
+        <v>0.957804945199484</v>
       </c>
       <c r="D52" t="n">
-        <v>0.2850816480352509</v>
+        <v>0.285621742820442</v>
       </c>
       <c r="E52" t="n">
-        <v>0.4301495684455391</v>
+        <v>0.4301418216908508</v>
       </c>
     </row>
     <row r="53">
@@ -1401,13 +1401,13 @@
         <v>0.8</v>
       </c>
       <c r="C53" t="n">
-        <v>0.9586458110944012</v>
+        <v>0.9568693887438472</v>
       </c>
       <c r="D53" t="n">
-        <v>0.288815921376763</v>
+        <v>0.289409383355337</v>
       </c>
       <c r="E53" t="n">
-        <v>0.4301952014931532</v>
+        <v>0.4306581143615943</v>
       </c>
     </row>
     <row r="54">
@@ -1418,13 +1418,13 @@
         <v>0.8</v>
       </c>
       <c r="C54" t="n">
-        <v>0.8080038879228831</v>
+        <v>0.8066932895144103</v>
       </c>
       <c r="D54" t="n">
-        <v>0.3064190582027788</v>
+        <v>0.3071253008621446</v>
       </c>
       <c r="E54" t="n">
-        <v>0.444416144514081</v>
+        <v>0.4452084377077061</v>
       </c>
     </row>
     <row r="55">
@@ -1435,13 +1435,13 @@
         <v>0.8</v>
       </c>
       <c r="C55" t="n">
-        <v>0.94114505353054</v>
+        <v>0.9433375658117268</v>
       </c>
       <c r="D55" t="n">
-        <v>0.2940240239744506</v>
+        <v>0.2949194459608292</v>
       </c>
       <c r="E55" t="n">
-        <v>0.4315709225331721</v>
+        <v>0.4324286581477654</v>
       </c>
     </row>
     <row r="56">
@@ -1452,13 +1452,13 @@
         <v>0.8</v>
       </c>
       <c r="C56" t="n">
-        <v>0.937391493164202</v>
+        <v>0.9552965280410748</v>
       </c>
       <c r="D56" t="n">
-        <v>0.2905735742159374</v>
+        <v>0.2920823829260906</v>
       </c>
       <c r="E56" t="n">
-        <v>0.4351289214193317</v>
+        <v>0.4336940666929859</v>
       </c>
     </row>
     <row r="57">
@@ -1469,13 +1469,13 @@
         <v>0.8</v>
       </c>
       <c r="C57" t="n">
-        <v>0.9348101186814074</v>
+        <v>0.919115290476224</v>
       </c>
       <c r="D57" t="n">
-        <v>0.2924552663552414</v>
+        <v>0.2964583948042589</v>
       </c>
       <c r="E57" t="n">
-        <v>0.4306606186046274</v>
+        <v>0.432526481838143</v>
       </c>
     </row>
     <row r="58">
@@ -1486,13 +1486,13 @@
         <v>0.8</v>
       </c>
       <c r="C58" t="n">
-        <v>0.9624911562464172</v>
+        <v>0.9646049994485127</v>
       </c>
       <c r="D58" t="n">
-        <v>0.2867185558040169</v>
+        <v>0.287267540884801</v>
       </c>
       <c r="E58" t="n">
-        <v>0.4269268810807945</v>
+        <v>0.427361105431417</v>
       </c>
     </row>
     <row r="59">
@@ -1503,13 +1503,13 @@
         <v>0.8</v>
       </c>
       <c r="C59" t="n">
-        <v>0.9743606710484726</v>
+        <v>0.9756422341811832</v>
       </c>
       <c r="D59" t="n">
-        <v>0.289133098843928</v>
+        <v>0.2897225180481565</v>
       </c>
       <c r="E59" t="n">
-        <v>0.4309291260763565</v>
+        <v>0.4313752020294187</v>
       </c>
     </row>
     <row r="60">
@@ -1520,13 +1520,13 @@
         <v>0.8</v>
       </c>
       <c r="C60" t="n">
-        <v>0.9687263239238506</v>
+        <v>0.9547822027168212</v>
       </c>
       <c r="D60" t="n">
-        <v>0.2866213252469111</v>
+        <v>0.2872914712670931</v>
       </c>
       <c r="E60" t="n">
-        <v>0.4272680305903716</v>
+        <v>0.4273018765954661</v>
       </c>
     </row>
     <row r="61">
@@ -1537,13 +1537,13 @@
         <v>0.8</v>
       </c>
       <c r="C61" t="n">
-        <v>0.9842226931196618</v>
+        <v>0.983427896140624</v>
       </c>
       <c r="D61" t="n">
-        <v>0.288160272560318</v>
+        <v>0.2885496673218862</v>
       </c>
       <c r="E61" t="n">
-        <v>0.4285729693665046</v>
+        <v>0.4288724114536998</v>
       </c>
     </row>
   </sheetData>
